--- a/files/output.xlsx
+++ b/files/output.xlsx
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>129581802867</t>
+          <t>131595781295</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -536,31 +536,36 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Взаперти</t>
+          <t>Форт Боярд</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Квесты;организация и проведение детских праздников;развлекательный центр</t>
+          <t>Организация и проведение детских праздников;квесты;организация мероприятий</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.900000095367432</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>157</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Казанская ул., 7, этаж -1</t>
+          <t>Кондратьевский просп., 2П, Санкт-Петербург</t>
         </is>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Скидка 10% в день звонка!</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -577,7 +582,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>205698480664</t>
+          <t>35853832811</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -587,7 +592,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -595,12 +600,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Взаперти</t>
+          <t>Кулинарные шоу CooknRun Events</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Квесты;организация мероприятий;организация и проведение детских праздников</t>
+          <t>Организация и проведение детских праздников;квесты;ведущие праздников и мероприятий;организация мероприятий</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -610,22 +615,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Соляной пер., 8, этаж 1, 3</t>
+          <t>Смольный просп., 9</t>
         </is>
       </c>
       <c r="J3" t="b">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Хорошее место 2025</t>
-        </is>
-      </c>
       <c r="M3" t="b">
         <v>0</v>
       </c>
@@ -636,7 +636,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7114784657</t>
+          <t>104642947127</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -654,31 +654,41 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Взаперти</t>
+          <t>Versus Reality</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Квесты;организация мероприятий;организация и проведение детских праздников</t>
+          <t>Клуб виртуальной реальности;квесты;организация и проведение детских праздников</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.599999904632568</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>746</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Загородный просп., 28, этаж цокольный</t>
+          <t>Большая Московская ул., 9</t>
         </is>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Скидка 20% в будни на посещение виртуальной реальности!</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Хорошее место 2025</t>
+        </is>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -690,7 +700,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>79754787585</t>
+          <t>1928475551</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -700,7 +710,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -708,12 +718,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Бассейн шариков</t>
+          <t>Портал-78</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Аттракцион;квесты;развлекательный центр</t>
+          <t>Организация и проведение детских праздников;квесты;лазертаг</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -723,28 +733,38 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>471</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Большая Морская ул., 3-5, Санкт-Петербург, этаж 1</t>
+          <t>ул. Чудновского, 10</t>
         </is>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1 час лазертага бесплатно для школьников с 1.09 по 10.10</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Хорошее место 2025</t>
+        </is>
       </c>
       <c r="M5" t="b">
         <v>0</v>
       </c>
       <c r="O5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>104642947127</t>
+          <t>48985153474</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -754,7 +774,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -762,47 +782,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Versus Reality</t>
+          <t>Иммерсивный театр Морфеус</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Клуб виртуальной реальности;квесты;организация и проведение детских праздников</t>
+          <t>Театр;квесты</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.800000190734863</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Большая Московская ул., 9</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Скидка 20% в будни на посещение виртуальной реальности!</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Хорошее место 2025</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
       </c>
       <c r="O6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -818,7 +823,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -833,7 +838,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>35853832811</t>
+          <t>226147946757</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -843,7 +848,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -851,29 +856,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Кулинарные шоу CooknRun Events</t>
+          <t>Urban Gaming</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Организация и проведение детских праздников;квесты;ведущие праздников и мероприятий;организация мероприятий</t>
+          <t>Развлекательный центр;организация и проведение детских праздников;лазертаг</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.800000190734863</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>169</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>226147946757</t>
+          <t>29842946332</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -883,7 +888,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -891,29 +896,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Urban Gaming</t>
+          <t>Игральня</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Развлекательный центр;организация и проведение детских праздников;лазертаг</t>
+          <t>Антикафе;кальян-бар;игровые приставки</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.800000190734863</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>922</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>48985153474</t>
+          <t>20751689239</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -931,29 +936,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Иммерсивный театр Морфеус</t>
+          <t>Комната ярости и снятия стресса</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Театр;квесты</t>
+          <t>Квесты;развлекательный центр;клуб досуга</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.800000190734863</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29842946332</t>
+          <t>3381507282</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -963,7 +968,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -971,12 +976,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Игральня</t>
+          <t>ILocked</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Антикафе;кальян-бар;игровые приставки</t>
+          <t>Квесты;организация мероприятий;организация и проведение детских праздников</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -986,14 +991,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>1048</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20751689239</t>
+          <t>205698480664</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1003,7 +1008,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1011,12 +1016,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Комната ярости и снятия стресса</t>
+          <t>Взаперти</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Квесты;развлекательный центр;клуб досуга</t>
+          <t>Квесты;организация мероприятий;организация и проведение детских праздников</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1026,14 +1031,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>940</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1928475551</t>
+          <t>166034250678</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1043,7 +1048,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1051,12 +1056,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Портал-78</t>
+          <t>Лабиринт страха</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Организация и проведение детских праздников;квесты;лазертаг</t>
+          <t>Квесты;парк аттракционов</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1066,14 +1071,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>662</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3381507282</t>
+          <t>218181428358</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1083,7 +1088,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1091,12 +1096,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ILocked</t>
+          <t>Шоу-игра Ринг</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Квесты;организация мероприятий;организация и проведение детских праздников</t>
+          <t>Квесты;развлекательный центр</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1106,14 +1111,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>166034250678</t>
+          <t>1724680630</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1123,7 +1128,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1131,12 +1136,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Лабиринт страха</t>
+          <t>Игра в Кальмара</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Квесты;парк аттракционов</t>
+          <t>Квесты;развлекательный центр</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1146,14 +1151,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>390</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1724680630</t>
+          <t>122826103520</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1163,7 +1168,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1171,12 +1176,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Игра в Кальмара</t>
+          <t>Квеструм.рф</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Квесты;развлекательный центр</t>
+          <t>Квесты;организация и проведение детских праздников;развлекательный центр</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1186,14 +1191,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>511</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>122826103520</t>
+          <t>11456557122</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1203,7 +1208,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1211,7 +1216,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Квеструм.рф</t>
+          <t>ILocked</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1226,14 +1231,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>1274</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11456557122</t>
+          <t>129581802867</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1243,7 +1248,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1251,7 +1256,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ILocked</t>
+          <t>Взаперти</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1266,7 +1271,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>457</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1288,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1323,7 +1328,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1363,7 +1368,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1403,7 +1408,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1443,7 +1448,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1483,7 +1488,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1523,7 +1528,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1563,7 +1568,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-09-22 22:08</t>
+          <t>2025-09-22 22:42</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1754,35 +1759,1010 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>131595781295</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, Кондратьевский проспект, 2П</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>30.374672</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>59.958806</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>+7 (812) 648-14-91</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://fort-boyard-spb.ru/?utm_medium=main&amp;utm_source=yandex_maps&amp;yclid=11728680150792667135</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-22:00
+Вт: 10:00-22:00
+Ср: 10:00-22:00
+Чт: 10:00-22:00
+Пт: 10:00-22:00
+Сб: 10:00-22:00
+Вс: 10:00-22:00</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>131</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>виды квестов: квесты, квесты с актерами, экшен-игры, с детьми, для новичков, веселые, для подростков, для больших компаний, для школьников, для корпоратива, для взрослых, по фильмам и играм, спортивные, соревновательные;корпоративные мероприятия: да;Оплата картой: да</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>https://yandex.ru/maps/org/fort_boyard/131595781295/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>35853832811</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, Смольный проспект, 9</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>30.393995</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>59.944084</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>+7 (812) 372-99-05</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://cookn.run/spb/?utm_source=яндекс.карты&amp;yclid=10221186903136272383</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Пн: 00:00-00:00
+Вт: 00:00-00:00
+Ср: 00:00-00:00
+Чт: 00:00-00:00
+Пт: 00:00-00:00
+Сб: 00:00-00:00
+Вс: 00:00-00:00</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>корпоративные мероприятия: да;Оплата картой: да;виды квестов: квесты, квесты с актерами, квизы, экшен-игры, с детьми, для новичков, веселые, для подростков, для больших компаний, для школьников, для корпоратива, для взрослых, динамичные, нестандартные, соревновательные, ролевые;доступность помещения на инвалидной коляске: недоступно;аквагрим: да;способ оплаты: наличными, оплата картой, безналичная, QR-код;организация свадеб: да;подарочный сертификат: да;доступность входа на инвалидной коляске: недоступно</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>https://yandex.ru/maps/org/kulinarnyye_shou_cooknrun_events/35853832811/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>104642947127</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, Большая Московская улица, 9</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>30.345783</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>59.926065</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+7 (911) 926-64-26+7 (812) 926-64-26</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://spb.versusvr.ru/?yclid=3862999968159629311&amp;utm_content=15790786926&amp;utm_source=geoadv_maps</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Пн: 11:00-23:00
+Вт: 12:00-22:00
+Ср: 12:00-22:00
+Чт: 12:00-22:00
+Пт: 12:00-22:00
+Сб: 11:00-23:00
+Вс: 11:00-23:00</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>191</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>посещение с животными: запрещено с животными;предварительная запись: да;авиасимулятор: да;доступность входа на инвалидной коляске: недоступно;способ оплаты: дисконтная система скидок, предоплата, наличными, оплата картой, электронными деньгами, банковским переводом, онлайн, СБП;Оплата картой: да;парковка: да;акции: скидки, акции, спецпредложения, бонусы, подарки;подарочный сертификат: да;онлайн-игры: да;персонал для мероприятий: да;Wi-Fi: да;доступность помещения на инвалидной коляске: недоступно;виды квестов: виртуальные квесты, виртуальная реальность, сложные, веселые, для подростков, детективные, мистические, нестандартные, приключения</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>https://yandex.ru/maps/org/versus_reality/104642947127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1928475551</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, улица Чудновского, 10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30.476236</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>59.92512</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+7 (812) 385-02-94</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://lazertagpiter.ru/?utm_source=yandex_maps&amp;yclid=6861477211235155967</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-22:00
+Вт: 10:00-22:00
+Ср: 10:00-22:00
+Чт: 10:00-22:00
+Пт: 10:00-22:00
+Сб: 10:00-22:00
+Вс: 10:00-22:00</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>376</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>аренда лофта: да;Оплата картой: да;персонал для мероприятий: да;аквагрим: да;акции: скидки, акции, спецпредложения;туалет: да;предварительная запись: да;парковка: да;подарочный сертификат: да</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>https://yandex.ru/maps/org/portal_78/1928475551/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>48985153474</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, набережная реки Мойки, 28</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>30.319902</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>59.938797</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+7 (977) 089-62-02</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://spb.morpheus-show.ru/?yclid=6169900873115238399&amp;utm_campaign=spb_setka_retarget&amp;utm_content=16558006889&amp;utm_medium=cpc&amp;utm_source=yandex&amp;utm_term=---autotargeting</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Пн: 12:00-23:00
+Вт: 17:00-23:30
+Ср: 19:00-23:30
+Чт: 17:00-23:30
+Пт: 19:00-23:30
+Сб: 15:00-23:30
+Вс: 12:00-23:00</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>88</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Оплата картой: да;театр: театр импровизации;посещение с животными: запрещено с животными;дата постройки: 2024;доступность входа на инвалидной коляске: недоступно;способ оплаты: оплата картой, онлайн;акции: спецпредложения;подарочный сертификат: да;Wi-Fi: да;билеты: 2600–3500 ₽;доступность помещения на инвалидной коляске: недоступно;виды квестов: для корпоратива</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>https://yandex.ru/maps/org/immersivny_teatr_morfeus/48985153474/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>30.332682</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>59.943331</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>226147946757</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, Арсенальная улица, 2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>30.373108</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>59.954918</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+7 (812) 926-35-28</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>http://urbangaming.ru/?yclid=4643615659958206463&amp;utm_campaign=113295085&amp;utm_content=16780210774&amp;utm_term=---autotargeting</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Пн: 00:00-00:00
+Вт: 00:00-00:00
+Ср: 00:00-00:00
+Чт: 00:00-00:00
+Пт: 00:00-00:00
+Сб: 00:00-00:00
+Вс: 00:00-00:00</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Оплата картой: да;парковка для людей с инвалидностью: да;доступность помещения на инвалидной коляске: частично доступно;способ оплаты: предоплата, наличными, оплата картой, банковским переводом, sms-платеж, рассрочка, безналичная, онлайн, QR-код, СБП, оплата кредитной картой, оформление кредита;акции: скидки, подарки;предварительная запись: да;Можно с собакой: да;подарочный сертификат: да;доступность входа на инвалидной коляске: доступно</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>29842946332</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, Гороховая улица, 23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>30.317543</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>59.93138</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+7 (921) 908-77-47, доб. 2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://igralnya.com/gorohovaya23/?utm_source=yandex_maps&amp;yclid=15187899076803297279</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Пн: 11:00-06:00
+Вт: 11:00-06:00
+Ср: 11:00-06:00
+Чт: 11:00-06:00
+Пт: 11:00-06:00
+Сб: 11:00-06:00
+Вс: 11:00-06:00</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>322</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>спортивные трансляции: да;подарочный сертификат: да;Чай: да;посещение с животными: разрешено со всеми животными;антикинотеатр: да;способ оплаты: дисконтная система скидок, наличными, оплата картой, банковским переводом, безналичная, онлайн, QR-код, СБП, оплата кредитной картой;Кофе: да;музыка: pop, chillout, фоновая;акции: скидки, акции, спецпредложения, бонусы, подарки;Зарядка для телефона: да;кнопка вызова персонала: да;Место для отдыха: да;туалет: да;Предзаказ онлайн: да;WC: да;предварительная запись: да;подписки на игровые сервисы: да;Оплата картой: да;парковка для людей с инвалидностью: да;Питьевая вода: да;доступность входа на инвалидной коляске: недоступно;Wi-Fi: да;аренда: да;тип заведения: чайный клуб, бар-клуб, пивной бар, лаунж-бар;марка игровой приставки: Sony PlayStation, Nintendo;доступность помещения на инвалидной коляске: недоступно;особенности заведения: настольные игры, барная стойка, можно с животными, можно с ноутбуком, игровые приставки;приглушенный свет: да;кинозал: да;настольные игры: да</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20751689239</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, улица Комсомола, 1-3АУ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>30.369264</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>59.956372</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>+7 (931) 211-62-00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://fury-room.ru/?yclid=9933352450676228095</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Пн: 12:00-21:00
+Вт: 12:00-21:00
+Ср: 12:00-21:00
+Чт: 12:00-21:00
+Пт: 12:00-21:00
+Сб: 12:00-21:00
+Вс: 12:00-21:00</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>52</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Оплата картой: да;виды квестов: перформансы, экшен-игры, для новичков, веселые, недорогие, для подростков, для больших компаний, для корпоратива, для взрослых, динамичные;посещение с животными: запрещено с животными;доступность помещения на инвалидной коляске: недоступно;способ оплаты: предоплата, постоплата, наличными, оплата картой, электронными деньгами, банковским переводом, безналичная, онлайн, QR-код, СБП, оплата кредитной картой, бесконтактная оплата;акции: скидки, акции, спецпредложения;парковка: бесплатная;Wi-Fi: да;велопарковка: да;предварительная запись: да;для детей: да;подарочный сертификат: да;доступность входа на инвалидной коляске: недоступно</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3381507282</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, Соляной переулок, 8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>30.341224</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>59.945387</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+7 (812) 448-68-94+7 (812) 565-16-94</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://ilocked.ru/</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-21:00
+Вт: 10:00-21:00
+Ср: 10:00-21:00
+Чт: 10:00-21:00
+Пт: 10:00-21:00
+Сб: 10:00-21:00
+Вс: 10:00-21:00</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>739</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>посещение с животными: запрещено с животными;организация свадеб: да;аренда лофта: да;доступность входа на инвалидной коляске: доступно;способ оплаты: скидки на услуги льготным категориям, дисконтная система скидок, предоплата, наличными, банковским переводом, sms-платеж, безналичная, онлайн;Оплата картой: да;корпоративные мероприятия: да;изготовление декораций: да;акции: скидки, акции, спецпредложения, бонусы, подарки;подарочный сертификат: да;аквагрим: да;персонал для мероприятий: да;Wi-Fi: да;доступность помещения на инвалидной коляске: недоступно;виды квестов: квесты, перформансы, квесты с актерами, квизы, экшен-игры, с детьми, для новичков, сложные, веселые, недорогие, для подростков, для больших компаний, для школьников, для корпоратива, исторические, для взрослых, детективные, динамичные, научные, мистические, нестандартные, по фильмам и играм, спортивные, соревновательные, приключения, страшные, гарри поттер, нестрашный, фантастический, для свиданий, антуражный;поздравления: аудио</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>205698480664</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, Соляной переулок, 8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>30.341164</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>59.945461</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>+7 (812) 566-45-48</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://vzaperti.net/catalog/kvesty-na-solanom</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-22:00
+Вт: 09:00-21:00
+Ср: 09:00-21:00
+Чт: 09:00-21:00
+Пт: 09:00-21:00
+Сб: 09:00-21:00
+Вс: 10:00-22:00</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>163</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>корпоративные мероприятия: да;аренда лофта: да;Оплата картой: да;виды квестов: квесты, перформансы, квесты с актерами, экшен-игры, с детьми, для новичков, сложные, веселые, для подростков, для больших компаний, для школьников, для корпоратива, для взрослых, динамичные, научные, по фильмам и играм, приключения;доступность помещения на инвалидной коляске: недоступно;аквагрим: да;способ оплаты: предоплата, постоплата;акции: скидки, спецпредложения;Wi-Fi: да;подарочный сертификат: да;доступность входа на инвалидной коляске: недоступно</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>166034250678</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, Невский проспект, 3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>30.312847</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>59.936805</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8 (800) 700-06-80+7 (965) 035-08-58</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://smile-park.ru/</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-22:00
+Вт: 10:00-22:00
+Ср: 10:00-22:00
+Чт: 10:00-22:00
+Пт: 10:00-22:00
+Сб: 10:00-22:00
+Вс: 10:00-22:00</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>121</v>
+      </c>
+      <c r="AA13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Оплата картой: да;виды квестов: квесты, квесты с актерами, экшен-игры, для новичков, недорогие, для подростков, для школьников, для корпоратива, для взрослых, динамичные, мистические, нестандартные, страшные;посещение с животными: запрещено с животными;доступность помещения на инвалидной коляске: недоступно;способ оплаты: предоплата, наличными, оплата картой, онлайн, QR-код, СБП;акции: скидки, акции, спецпредложения, подарки;предварительная запись: да;подарочный сертификат: да;доступность входа на инвалидной коляске: недоступно</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>218181428358</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, улица Комсомола, 2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>30.370045</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>59.954852</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>+7 (812) 501-10-02</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://show-ring.ru/?yclid=9926190335389859839&amp;utm_campaign=701090132&amp;utm_content=17112869210&amp;utm_medium=cpc&amp;utm_source=yandex&amp;utm_term=---autotargeting</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-02:00
+Вт: 10:00-02:00
+Ср: 10:00-02:00
+Чт: 10:00-02:00
+Пт: 10:00-02:00
+Сб: 10:00-02:00
+Вс: 10:00-02:00</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>94</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>виды квестов: квесты, квизы, экшен-игры, с детьми, для новичков, веселые, недорогие, для подростков, для больших компаний, для школьников, для корпоратива, для взрослых, динамичные, нестандартные, соревновательные;для детей: да;парковка: да;акции: акции, спецпредложения;Wi-Fi: да;способ оплаты: предоплата, постоплата, наличными, банковским переводом, безналичная</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1724680630</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, набережная Кутузова, 30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>30.339341</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>59.948356</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>+7 (921) 905-52-98</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://generoom.ru/</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-22:30
+Вт: 09:00-22:30
+Ср: 09:00-22:30
+Чт: 09:00-22:30
+Пт: 09:00-22:30
+Сб: 09:00-22:30
+Вс: 09:00-22:30</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>215</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>посещение с животными: запрещено с животными;предварительная запись: да;парковка: платная;доступность входа на инвалидной коляске: недоступно;способ оплаты: наличными, оплата картой, электронными деньгами, QR-код;подарочный сертификат: да;для детей: да;велопарковка: да;Можно с собакой: да;доступность помещения на инвалидной коляске: недоступно;виды квестов: квесты, квесты с актерами, с детьми, для новичков, сложные, недорогие, для подростков, для больших компаний, для школьников, для корпоратива, для взрослых, научные, нестандартные, по фильмам и играм, соревновательные, приключения, фантастический, антуражный</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>122826103520</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, Конюшенная площадь, 2В</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>30.325424</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>59.940034</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>+7 (812) 407-22-58+7 (812) 245-69-67</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>http://спб.квеструм.рф/</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-23:00
+Вт: 12:00-23:00
+Ср: 12:00-23:00
+Чт: 12:00-23:00
+Пт: 12:00-23:00
+Сб: 12:00-23:00
+Вс: 10:00-23:00</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>136</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>аренда лофта: да;персонал для мероприятий: да;виды квестов: квесты, перформансы, квесты с актерами, квизы, экшен-игры, с детьми, для новичков, сложные, веселые, недорогие, для подростков, для больших компаний, для школьников, для корпоратива, для взрослых, детективные, динамичные, научные, ограбление, мистические, нестандартные, по фильмам и играм, соревновательные, приключения, тюремные, страшные, нестрашный, фантастический, для свиданий, антуражный;посещение с животными: запрещено с животными;доступность помещения на инвалидной коляске: недоступно;способ оплаты: дисконтная система скидок, предоплата, наличными, банковским переводом, онлайн;акции: скидки, акции, спецпредложения;парковка: бесплатная;Wi-Fi: да;велопарковка: да;предварительная запись: да;кафе: да;парковка: да;для детей: да;подарочный сертификат: да;доступность входа на инвалидной коляске: недоступно</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>11456557122</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, Александровский парк, 4к3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>30.314788</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>59.956262</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>+7 (812) 448-68-94+7 (812) 605-99-29+7 (812) 998-38-27</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://velikanpark.ilocked.ru/;https://ilocked.ru/</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-22:00
+Вт: 10:00-22:00
+Ср: 10:00-22:00
+Чт: 10:00-22:00
+Пт: 10:00-22:00
+Сб: 10:00-22:00
+Вс: 10:00-22:00</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>703</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>посещение с животными: запрещено с животными;аренда лофта: да;парковка: платная;доступность входа на инвалидной коляске: недоступно;способ оплаты: скидки на услуги льготным категориям, дисконтная система скидок, предоплата, наличными, оплата картой, sms-платеж, безналичная, онлайн, СБП;Оплата картой: да;парковка: да;акции: скидки, акции, спецпредложения, бонусы, подарки;подарочный сертификат: да;для детей: да;велопарковка: да;аквагрим: да;персонал для мероприятий: да;Wi-Fi: да;доступность помещения на инвалидной коляске: недоступно;виды квестов: квесты, квесты с актерами, экшен-игры, для новичков, сложные, недорогие, для подростков, для школьников, для корпоратива, мистические, по фильмам и играм, приключения;поздравления: аудио</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>129581802867</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Санкт-Петербург, Казанская улица, 7</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>30.321484</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>59.932458</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>+7 (812) 566-45-48</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>http://vzaperti.net/?yclid=4916111006268391423&amp;utm_campaign=115778456&amp;utm_content=16783861395&amp;utm_medium=cpc&amp;utm_source=yandex&amp;utm_term=---autotargeting</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>http://vzaperti.net/</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Пн: 11:00-21:00
 Вт: 11:00-21:00
@@ -1793,987 +2773,18 @@
 Вс: 11:00-21:00</t>
         </is>
       </c>
-      <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
         <v>55</v>
       </c>
-      <c r="AA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AA18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>посещение с животными: запрещено с животными;предварительная запись: да;аренда лофта: да;парковка: платная;доступность входа на инвалидной коляске: недоступно;способ оплаты: скидки на услуги льготным категориям, дисконтная система скидок, наличными, оплата картой, электронными деньгами, банковским переводом, безналичная;Оплата картой: да;акции: скидки, спецпредложения, бонусы;подарочный сертификат: да;для детей: да;аквагрим: да;Wi-Fi: да;доступность помещения на инвалидной коляске: доступно;виды квестов: квесты, перформансы, квесты с актерами, квизы, с детьми, для новичков, веселые, недорогие, для подростков, для больших компаний, для школьников, для корпоратива, для взрослых, динамичные, тюремные</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>https://yandex.ru/maps/org/vzaperti/129581802867/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>205698480664</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Соляной переулок, 8</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>30.341164</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>59.945461</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>+7 (812) 566-45-48</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://vzaperti.net/catalog/kvesty-na-solanom?yclid=3332942880095076351&amp;utm_campaign=115778456&amp;utm_content=17088418217&amp;utm_medium=cpc&amp;utm_source=yandex&amp;utm_term=---autotargeting</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-22:00
-Вт: 09:00-21:00
-Ср: 09:00-21:00
-Чт: 09:00-21:00
-Пт: 09:00-21:00
-Сб: 09:00-21:00
-Вс: 10:00-22:00</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>163</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>корпоративные мероприятия: да;аренда лофта: да;Оплата картой: да;виды квестов: квесты, перформансы, квесты с актерами, экшен-игры, с детьми, для новичков, сложные, веселые, для подростков, для больших компаний, для школьников, для корпоратива, для взрослых, динамичные, научные, по фильмам и играм, приключения;доступность помещения на инвалидной коляске: недоступно;аквагрим: да;способ оплаты: предоплата, постоплата;акции: скидки, спецпредложения;Wi-Fi: да;подарочный сертификат: да;доступность входа на инвалидной коляске: недоступно</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>https://yandex.ru/maps/org/vzaperti/205698480664/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>7114784657</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Загородный проспект, 28</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>30.339798</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>59.924818</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>+7 (812) 566-45-48</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>http://vzaperti.net/?yclid=13297999505860853759&amp;utm_campaign=115778456&amp;utm_content=17093916723&amp;utm_medium=cpc&amp;utm_source=yandex&amp;utm_term=---autotargeting</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Пн: 12:00-22:00
-Вт: 12:00-22:00
-Ср: 12:00-22:00
-Чт: 12:00-22:00
-Пт: 12:00-22:00
-Сб: 12:00-22:00
-Вс: 12:00-22:00</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>посещение с животными: запрещено с животными;предварительная запись: да;Wi-Fi: да;подарочный сертификат: да;способ оплаты: наличными, предоплата, СБП;доступность входа на инвалидной коляске: недоступно</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>https://yandex.ru/maps/org/vzaperti/7114784657/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>79754787585</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Большая Морская улица, 3-5</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>30.31737</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>59.937211</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>8 (800) 700-06-80+7 (965) 035-08-58</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://smile-park.ru/?yclid=3147016198822821887&amp;utm_content=15790818551&amp;utm_source=geoadv_maps</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-22:00
-Вт: 10:00-22:00
-Ср: 10:00-22:00
-Чт: 10:00-22:00
-Пт: 10:00-22:00
-Сб: 10:00-22:00
-Вс: 10:00-22:00</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>81</v>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>посещение с животными: запрещено с животными;предварительная запись: да;парковка: платная;доступность входа на инвалидной коляске: недоступно;способ оплаты: предоплата, наличными, оплата картой, онлайн, оплата кредитной картой;Оплата картой: да;парковка: да;акции: скидки, акции, спецпредложения, бонусы, подарки;подарочный сертификат: да;для детей: да;комната ярости: да;Wi-Fi: да;доступность помещения на инвалидной коляске: недоступно;виды квестов: квесты, квесты с актерами, с детьми, для новичков, веселые, недорогие, для подростков, для больших компаний, для школьников, для корпоратива, детективные, ограбление, тюремные, комната ярости</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>https://yandex.ru/maps/org/basseyn_sharikov/79754787585/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>104642947127</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Большая Московская улица, 9</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>30.345783</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>59.926065</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>+7 (911) 926-64-26+7 (812) 926-64-26</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://spb.versusvr.ru/?yclid=14640189022223204351&amp;utm_content=15790786926&amp;utm_source=geoadv_maps</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Пн: 11:00-23:00
-Вт: 12:00-22:00
-Ср: 12:00-22:00
-Чт: 12:00-22:00
-Пт: 12:00-22:00
-Сб: 11:00-23:00
-Вс: 11:00-23:00</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>191</v>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>посещение с животными: запрещено с животными;предварительная запись: да;авиасимулятор: да;доступность входа на инвалидной коляске: недоступно;способ оплаты: дисконтная система скидок, предоплата, наличными, оплата картой, электронными деньгами, банковским переводом, онлайн, СБП;Оплата картой: да;парковка: да;акции: скидки, акции, спецпредложения, бонусы, подарки;подарочный сертификат: да;онлайн-игры: да;персонал для мероприятий: да;Wi-Fi: да;доступность помещения на инвалидной коляске: недоступно;виды квестов: виртуальные квесты, виртуальная реальность, сложные, веселые, для подростков, детективные, мистические, нестандартные, приключения</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>https://yandex.ru/maps/org/versus_reality/104642947127/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>30.332682</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>59.943331</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>35853832811</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Смольный проспект, 9</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>30.393995</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>59.944084</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>+7 (812) 372-99-05</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://cookn.run/spb/?utm_source=яндекс.карты&amp;yclid=3602365230550876159</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Пн: 00:00-00:00
-Вт: 00:00-00:00
-Ср: 00:00-00:00
-Чт: 00:00-00:00
-Пт: 00:00-00:00
-Сб: 00:00-00:00
-Вс: 00:00-00:00</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>корпоративные мероприятия: да;Оплата картой: да;виды квестов: квесты, квесты с актерами, квизы, экшен-игры, с детьми, для новичков, веселые, для подростков, для больших компаний, для школьников, для корпоратива, для взрослых, динамичные, нестандартные, соревновательные, ролевые;доступность помещения на инвалидной коляске: недоступно;аквагрим: да;способ оплаты: наличными, оплата картой, безналичная, QR-код;организация свадеб: да;подарочный сертификат: да;доступность входа на инвалидной коляске: недоступно</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>226147946757</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Арсенальная улица, 2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>30.373108</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>59.954918</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>+7 (812) 926-35-28</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>http://urbangaming.ru/?yclid=14541973122004025343&amp;utm_campaign=113295085&amp;utm_content=16780210729&amp;utm_term=---autotargeting</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Пн: 00:00-00:00
-Вт: 00:00-00:00
-Ср: 00:00-00:00
-Чт: 00:00-00:00
-Пт: 00:00-00:00
-Сб: 00:00-00:00
-Вс: 00:00-00:00</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>42</v>
-      </c>
-      <c r="K9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Оплата картой: да;парковка для людей с инвалидностью: да;доступность помещения на инвалидной коляске: частично доступно;способ оплаты: предоплата, наличными, оплата картой, банковским переводом, sms-платеж, рассрочка, безналичная, онлайн, QR-код, СБП, оплата кредитной картой, оформление кредита;акции: скидки, подарки;предварительная запись: да;Можно с собакой: да;подарочный сертификат: да;доступность входа на инвалидной коляске: доступно</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>48985153474</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, набережная реки Мойки, 28</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>30.319902</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>59.938797</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>+7 (977) 089-62-02</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://spb.morpheus-show.ru/?yclid=8784694161502109695&amp;utm_campaign=b2bspb&amp;utm_content=17192716390&amp;utm_medium=cpc&amp;utm_source=yandex&amp;utm_term=---autotargeting</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Пн: 12:00-23:00
-Вт: 17:00-23:30
-Ср: 19:00-23:30
-Чт: 17:00-23:30
-Пт: 19:00-23:30
-Сб: 15:00-23:30
-Вс: 12:00-23:00</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>88</v>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Оплата картой: да;театр: театр импровизации;посещение с животными: запрещено с животными;дата постройки: 2024;доступность входа на инвалидной коляске: недоступно;способ оплаты: оплата картой, онлайн;акции: спецпредложения;подарочный сертификат: да;Wi-Fi: да;билеты: 2600–3500 ₽;доступность помещения на инвалидной коляске: недоступно;виды квестов: для корпоратива</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>29842946332</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Гороховая улица, 23</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>30.317543</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>59.93138</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>+7 (921) 908-77-47, доб. 2</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://igralnya.com/gorohovaya23/?utm_source=yandex_maps&amp;yclid=8823281245674536959</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Пн: 11:00-06:00
-Вт: 11:00-06:00
-Ср: 11:00-06:00
-Чт: 11:00-06:00
-Пт: 11:00-06:00
-Сб: 11:00-06:00
-Вс: 11:00-06:00</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>322</v>
-      </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>спортивные трансляции: да;подарочный сертификат: да;Чай: да;посещение с животными: разрешено со всеми животными;антикинотеатр: да;способ оплаты: дисконтная система скидок, наличными, оплата картой, банковским переводом, безналичная, онлайн, QR-код, СБП, оплата кредитной картой;Кофе: да;музыка: pop, chillout, фоновая;акции: скидки, акции, спецпредложения, бонусы, подарки;Зарядка для телефона: да;кнопка вызова персонала: да;Место для отдыха: да;туалет: да;Предзаказ онлайн: да;WC: да;предварительная запись: да;подписки на игровые сервисы: да;Оплата картой: да;парковка для людей с инвалидностью: да;Питьевая вода: да;доступность входа на инвалидной коляске: недоступно;Wi-Fi: да;аренда: да;тип заведения: чайный клуб, бар-клуб, пивной бар, лаунж-бар;марка игровой приставки: Sony PlayStation, Nintendo;доступность помещения на инвалидной коляске: недоступно;особенности заведения: настольные игры, барная стойка, можно с животными, можно с ноутбуком, игровые приставки;приглушенный свет: да;кинозал: да;настольные игры: да</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>20751689239</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, улица Комсомола, 1-3АУ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>30.369264</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>59.956372</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>+7 (931) 211-62-00</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://fury-room.ru/?yclid=8905194215145471999</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Пн: 12:00-21:00
-Вт: 12:00-21:00
-Ср: 12:00-21:00
-Чт: 12:00-21:00
-Пт: 12:00-21:00
-Сб: 12:00-21:00
-Вс: 12:00-21:00</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>52</v>
-      </c>
-      <c r="K12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Оплата картой: да;виды квестов: перформансы, экшен-игры, для новичков, веселые, недорогие, для подростков, для больших компаний, для корпоратива, для взрослых, динамичные;посещение с животными: запрещено с животными;доступность помещения на инвалидной коляске: недоступно;способ оплаты: предоплата, постоплата, наличными, оплата картой, электронными деньгами, банковским переводом, безналичная, онлайн, QR-код, СБП, оплата кредитной картой, бесконтактная оплата;акции: скидки, акции, спецпредложения;парковка: бесплатная;Wi-Fi: да;велопарковка: да;предварительная запись: да;для детей: да;подарочный сертификат: да;доступность входа на инвалидной коляске: недоступно</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1928475551</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, улица Чудновского, 10</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>30.476236</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>59.92512</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>+7 (812) 385-02-94</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://lazertagpiter.ru/?utm_source=yandex_maps&amp;yclid=3082954440077213695</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-22:00
-Вт: 10:00-22:00
-Ср: 10:00-22:00
-Чт: 10:00-22:00
-Пт: 10:00-22:00
-Сб: 10:00-22:00
-Вс: 10:00-22:00</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>376</v>
-      </c>
-      <c r="K13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>аренда лофта: да;Оплата картой: да;персонал для мероприятий: да;аквагрим: да;акции: скидки, акции, спецпредложения;туалет: да;предварительная запись: да;парковка: да;подарочный сертификат: да</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>3381507282</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Соляной переулок, 8</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>30.341224</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>59.945387</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>+7 (812) 448-68-94+7 (812) 565-16-94</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://ilocked.ru/</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-21:00
-Вт: 10:00-21:00
-Ср: 10:00-21:00
-Чт: 10:00-21:00
-Пт: 10:00-21:00
-Сб: 10:00-21:00
-Вс: 10:00-21:00</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>739</v>
-      </c>
-      <c r="K14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>посещение с животными: запрещено с животными;организация свадеб: да;аренда лофта: да;доступность входа на инвалидной коляске: доступно;способ оплаты: скидки на услуги льготным категориям, дисконтная система скидок, предоплата, наличными, банковским переводом, sms-платеж, безналичная, онлайн;Оплата картой: да;корпоративные мероприятия: да;изготовление декораций: да;акции: скидки, акции, спецпредложения, бонусы, подарки;подарочный сертификат: да;аквагрим: да;персонал для мероприятий: да;Wi-Fi: да;доступность помещения на инвалидной коляске: недоступно;виды квестов: квесты, перформансы, квесты с актерами, квизы, экшен-игры, с детьми, для новичков, сложные, веселые, недорогие, для подростков, для больших компаний, для школьников, для корпоратива, исторические, для взрослых, детективные, динамичные, научные, мистические, нестандартные, по фильмам и играм, спортивные, соревновательные, приключения, страшные, гарри поттер, нестрашный, фантастический, для свиданий, антуражный;поздравления: аудио</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>166034250678</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Невский проспект, 3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>30.312847</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>59.936805</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>8 (800) 700-06-80+7 (965) 035-08-58</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://smile-park.ru/</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-22:00
-Вт: 10:00-22:00
-Ср: 10:00-22:00
-Чт: 10:00-22:00
-Пт: 10:00-22:00
-Сб: 10:00-22:00
-Вс: 10:00-22:00</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>121</v>
-      </c>
-      <c r="AA15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Оплата картой: да;виды квестов: квесты, квесты с актерами, экшен-игры, для новичков, недорогие, для подростков, для школьников, для корпоратива, для взрослых, динамичные, мистические, нестандартные, страшные;посещение с животными: запрещено с животными;доступность помещения на инвалидной коляске: недоступно;способ оплаты: предоплата, наличными, оплата картой, онлайн, QR-код, СБП;акции: скидки, акции, спецпредложения, подарки;предварительная запись: да;подарочный сертификат: да;доступность входа на инвалидной коляске: недоступно</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1724680630</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, набережная Кутузова, 30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>30.339341</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>59.948356</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>+7 (921) 905-52-98</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://generoom.ru/</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-22:30
-Вт: 09:00-22:30
-Ср: 09:00-22:30
-Чт: 09:00-22:30
-Пт: 09:00-22:30
-Сб: 09:00-22:30
-Вс: 09:00-22:30</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>215</v>
-      </c>
-      <c r="K16" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>посещение с животными: запрещено с животными;предварительная запись: да;парковка: платная;доступность входа на инвалидной коляске: недоступно;способ оплаты: наличными, оплата картой, электронными деньгами, QR-код;подарочный сертификат: да;для детей: да;велопарковка: да;Можно с собакой: да;доступность помещения на инвалидной коляске: недоступно;виды квестов: квесты, квесты с актерами, с детьми, для новичков, сложные, недорогие, для подростков, для больших компаний, для школьников, для корпоратива, для взрослых, научные, нестандартные, по фильмам и играм, соревновательные, приключения, фантастический, антуражный</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>122826103520</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Конюшенная площадь, 2В</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>30.325424</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>59.940034</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>+7 (812) 407-22-58+7 (812) 245-69-67</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>http://спб.квеструм.рф/</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-23:00
-Вт: 12:00-23:00
-Ср: 12:00-23:00
-Чт: 12:00-23:00
-Пт: 12:00-23:00
-Сб: 12:00-23:00
-Вс: 10:00-23:00</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>136</v>
-      </c>
-      <c r="K17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>аренда лофта: да;персонал для мероприятий: да;виды квестов: квесты, перформансы, квесты с актерами, квизы, экшен-игры, с детьми, для новичков, сложные, веселые, недорогие, для подростков, для больших компаний, для школьников, для корпоратива, для взрослых, детективные, динамичные, научные, ограбление, мистические, нестандартные, по фильмам и играм, соревновательные, приключения, тюремные, страшные, нестрашный, фантастический, для свиданий, антуражный;посещение с животными: запрещено с животными;доступность помещения на инвалидной коляске: недоступно;способ оплаты: дисконтная система скидок, предоплата, наличными, банковским переводом, онлайн;акции: скидки, акции, спецпредложения;парковка: бесплатная;Wi-Fi: да;велопарковка: да;предварительная запись: да;кафе: да;парковка: да;для детей: да;подарочный сертификат: да;доступность входа на инвалидной коляске: недоступно</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>11456557122</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Александровский парк, 4к3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>30.314788</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>59.956262</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>+7 (812) 448-68-94+7 (812) 605-99-29+7 (812) 998-38-27</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://velikanpark.ilocked.ru/;https://ilocked.ru/</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-22:00
-Вт: 10:00-22:00
-Ср: 10:00-22:00
-Чт: 10:00-22:00
-Пт: 10:00-22:00
-Сб: 10:00-22:00
-Вс: 10:00-22:00</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>703</v>
-      </c>
-      <c r="K18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>посещение с животными: запрещено с животными;аренда лофта: да;парковка: платная;доступность входа на инвалидной коляске: недоступно;способ оплаты: скидки на услуги льготным категориям, дисконтная система скидок, предоплата, наличными, оплата картой, sms-платеж, безналичная, онлайн, СБП;Оплата картой: да;парковка: да;акции: скидки, акции, спецпредложения, бонусы, подарки;подарочный сертификат: да;для детей: да;велопарковка: да;аквагрим: да;персонал для мероприятий: да;Wi-Fi: да;доступность помещения на инвалидной коляске: недоступно;виды квестов: квесты, квесты с актерами, экшен-игры, для новичков, сложные, недорогие, для подростков, для школьников, для корпоратива, мистические, по фильмам и играм, приключения;поздравления: аудио</t>
         </is>
       </c>
     </row>
